--- a/data/enobnu/asistencia/asistencia_enobnu.xlsx
+++ b/data/enobnu/asistencia/asistencia_enobnu.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -736,7 +736,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Mondaca Rivera, José Ignacio</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -757,6 +757,656 @@
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Salas Galaz, Juan Carlos</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Aguiló Roa, Laura Andrea</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Aravena Bello, Fernanda Ignacia</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Badilla Carvallo, Vicente Luciano</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Carrasco Cea, María José</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr"/>
+      <c r="S12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Contreras Díaz, Paola Magdalena</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Fernández Arce, Martina Antonella</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>González Pastene, Kiara Pilar</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>González Valdebenito, Alexander Bryan</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hernández Olivares, Nicole Fernanda</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Isla Vega, Catalina Abril</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Lacoste Muñoz, Rosario Emilia</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Mardones Aránguiz, Agustina Ignacia</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Mendoza Azócar, Vania Fernanda</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Molina Cornejo, Lindsey Scarlett</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Moraga Michea, Mariana Constanza</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Morales Soto, Marlys Fernanda</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+      <c r="S24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Navarro Céspedes, Javiera Carolina</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Pavez Jaure, Laura Antonella</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Pavez Liendo, Amara Ignacia</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Rubio Ríos, Sofía Emilia</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Santibáñez Ruz, Antonia Ignacia</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Vergara Ramírez, Anaís Elisa</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
+      <c r="S30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Villarroel González, Fernanda Isidora</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr"/>
+      <c r="S31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Villaseca Fernández, Olivia</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr"/>
+      <c r="S32" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
@@ -1526,7 +2176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1768,7 +2418,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Bernal Santibáñez, Maximiliano Adolfo</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -1790,6 +2440,681 @@
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Salas Galaz, Juan Carlos</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Aguirre Gaspar, Fernanda Valentina</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Arévalo González, Josefa Belen</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Castillo Rodríguez, Ayleen Scarlet</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Catalán Riquelme, Valentina Alejandra</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr"/>
+      <c r="S12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Espinoza Varas, Gabriela Ignacia</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Fica Aguayo, Catalina Rayen</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Figueroa Fuentes, Alexander Christian Rudy</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Gallardo Noriega, Daniela Patricia</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Garrido Caniullán, Francisca Almendra</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Garrido Leiva, Isabel Elena</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Geminiani Campos, Nicoletta Aracelli</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Guerra Queralto, Antonia Elba</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Inda Kendall, Marializ Scarleth</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Lara Sandoval, Valentina Francisca</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Letelier Salgado, Anais Belen</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Llaulén Torres, Camila Fernanda</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+      <c r="S24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Mutis Montenegro, Isidora Ailin</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Naranjo Chandía, Ayelén Constanza</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Parada Caripillan, Nayra Sofía</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Reyes González, Ernesto Javier</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Reyes González, Rocío Nazareth</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Soto Muñoz, Javiera Paz</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
+      <c r="S30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Terrazas Benítez, Yamila Andrea</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr"/>
+      <c r="S31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Valdebenito Gómez, Daphne Antonella</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr"/>
+      <c r="S32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Zuloaga Flores, Bárbara Javiera</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="R33" s="5" t="inlineStr"/>
+      <c r="S33" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1802,7 +3127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2044,7 +3369,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Brancacho Chung, Valeria May</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -2065,6 +3390,656 @@
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Salas Galaz, Juan Carlos</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Aguayo Torres, Pamela Micaela</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Alarcón Cofré, Carla Millaray</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Bruna Brown, Catalina Soledad Alfonsina</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Donoso Álvarez, Nazaret Berenice</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr"/>
+      <c r="S12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Escobedo Guevara, Carolina Daniela</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Espínola De la Rivera, Isidora Valentina</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Fuentes Reuca, Angel Eliezer</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Gajardo San Martín, María Emilia</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Gassols Jiménez, Fernanda Pascale</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Guevara Ardiles, María Ignacia</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Herrera Yevilao, Meyling Isidora</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Landeros Vargas, Eluney Josefina</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Marquez Bermudez, Luis Alejandro</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Miranda Muñoz, Amanda de Jesús</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Navarrete Carrasco, Constanza Ignacia</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Nuñez Sanchez, Javiera Almudena</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+      <c r="S24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Orellana Hidalgo, Fernanda Catalina</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Ortega Gómez, Martina Isidora</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Ortega Placencia, Aracelly Belén</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Patricio Felix, Jhanira Fernanda</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Román Carrasco, Martín Ismael</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Sáez Lazo, Valentina Ignacia</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
+      <c r="S30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Salinas Franchini, Martina Ignacia</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr"/>
+      <c r="S31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>San Martín Vera, Camila Antonia</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr"/>
+      <c r="S32" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
@@ -2834,7 +4809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3054,7 +5029,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Galaz Paredes, Ingrid Del Pilar</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -3074,6 +5049,627 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Hidalgo Rojas, Diego Mauricio</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Aguirre Díaz, María José Beatriz</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Cabrera Martínez, Ignacia Paz</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Cerda Mardones, Benjamín Ignacio</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Cortés Escárate, Javiera Constanza</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Cuevas Figueroa, Paula Patricia</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Escanilla Becerra, Isabella Andrea</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Fuentealba Delgadillo, Anahy Alexandra Millarau</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Fuentes Vélez, Belen Anais</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hernández Escobar, Tamara Belén</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Jamasmie Delucchi, Rafaella Nahllat</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Jara Gajardo, Catalina</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Leal Venegas, Agustina Antonia</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Licanqueo Arredondo, Paula Ignacia</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Lobos Valenzuela, Fernanda Valentina</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Montenegro Acuña, Martín Tomás</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Rivas Muñoz, Renato Agustin</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Rodríguez Calderón, Isidora Paz</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Sobarzo Barra, Fernanda Emilia</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Tobar Uribe, Javiera Ignacia</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Toro Torres, Octavia Paz</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Trujillo Hernández, Emilia Antonia</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Urbina Medina, Fernanda Antonia</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Villalobos Martínez, Abril Danae</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Villegas González, Camila Antonia</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Zúñiga Pizarro, Catalina Paz</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3086,7 +5682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3306,7 +5902,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Galaz Paredes, Ingrid Del Pilar</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -3326,6 +5922,604 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Martinez Garrido, Gabriela Alejandra</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Ahumada Quintanilla, Catalina Antonia</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Alcozer Hidalgo, Amanda Lis</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Aranda Acosta, Catalina Andrea</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Cancino Badilla, Fernanda Josefa</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Castillo Pavez, Valentina Anaís</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Castro Castro, Ignacia Antonia</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Cerda Otárola, Octavio Ismael</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Condemarín Valenzuela, Catalina Ignacia</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Duarte González, Vicente Ignacio</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Ferreyra Aliste, Sofía Catalina</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>García Painel, Nicolás Agustín</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>González Perona, Isis Amapola</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Heyl González, Camila Ignacia</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Lefiche Trafiñanco, Rocío Belén</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Mardones Matamala, Antonia Esperanza</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Millacoy Herrera, Sofía Ignacia</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Mora Vergara, Anaís Alejandra</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Núñez Cuevas, Camila Isidora Madelaine</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Pardo Silva, Milena Antonia</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Riquelme Montepil, Anaís Esperanza Cristina</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Servieres Osorio, Sofía Matilda</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Trujillo Almiray, Elizabeth Beatriz Carolina</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Valenzuela Arriaza, María Pía</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Vergara Coloma, Bianca Antonia</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3338,7 +6532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3558,7 +6752,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Bernal Santibáñez, Maximiliano Adolfo</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -3578,6 +6772,650 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Galaz Paredes, Ingrid Del Pilar</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Águila Inaicheo, Cristopher Nicolás</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Araya Isla, Javiera Rayén</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Blanco Rattia, Camila Valentina</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Chavez Azañero, Keity Mireya</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>De la Fuente Ardiles, Maria Jesus Ignacia</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Figueroa González, Teresa Sofía</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Flock Bozzo, Fiona</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Hernández León, Maximiliano Ignacio</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Jara Jara, Aracely Andrea</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Kimura Heredia, Suimin Aiko</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Larez Montilla, Tino Alejandro</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>León Maturana, María Jesús</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Mendez Betancourt, Marianny Amada</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Muñoz Heredia, Renata Fabiola</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Quintana Becerra, Rocío Aurora</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Rojas Alvarez, Mayre Alejandra</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Santibáñez Herrera, Anaís Constanza</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Tabilo Cortés, Angelina Antonella</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Toro Toro, Yostin Ignacio</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Torres Reyes, Martina Isidora</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Urra Tapia, Kendra Martina</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Urrutia Díaz, Josefa Paz</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Valdivia Flores, Nicole Andrea Masiel</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Valenzuela Morales, María Fernanda</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Vásquez González, Antonia Leonor</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Jiménez, María Ignacia</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
